--- a/01-tavares-claims-grc-program/artifacts/risk_register.xlsx
+++ b/01-tavares-claims-grc-program/artifacts/risk_register.xlsx
@@ -558,6 +558,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="35.05" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -759,7 +760,7 @@
       </c>
       <c r="U5" s="15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="V5" s="15" t="inlineStr">
@@ -857,7 +858,7 @@
       </c>
       <c r="U6" s="15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="V6" s="15" t="inlineStr">
@@ -874,7 +875,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -955,7 +956,7 @@
       </c>
       <c r="U7" s="15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="V7" s="15" t="inlineStr">
@@ -1053,7 +1054,7 @@
       </c>
       <c r="U8" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="V8" s="15" t="inlineStr">
@@ -1151,7 +1152,7 @@
       </c>
       <c r="U9" s="15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="V9" s="15" t="inlineStr">
@@ -1249,7 +1250,7 @@
       </c>
       <c r="U10" s="15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="V10" s="15" t="inlineStr">
@@ -1445,7 +1446,7 @@
       </c>
       <c r="U12" s="15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="V12" s="15" t="inlineStr">
@@ -1462,7 +1463,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1543,7 +1544,7 @@
       </c>
       <c r="U13" s="15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="V13" s="15" t="inlineStr">
@@ -1641,7 +1642,7 @@
       </c>
       <c r="U14" s="15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="V14" s="15" t="inlineStr">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="U15" s="15" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="V15" s="15" t="inlineStr">
@@ -1837,7 +1838,7 @@
       </c>
       <c r="U16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="V16" s="15" t="inlineStr">
@@ -1854,7 +1855,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1935,7 +1936,7 @@
       </c>
       <c r="U17" s="15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="V17" s="15" t="inlineStr">
@@ -2033,7 +2034,7 @@
       </c>
       <c r="U18" s="15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="V18" s="15" t="inlineStr">
@@ -2131,7 +2132,7 @@
       </c>
       <c r="U19" s="15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="V19" s="15" t="inlineStr">
@@ -2173,7 +2174,7 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Notification window negotiated before Tavares set an internal 72-hour vendor standard; contract auto-renewed 2026-01-15 on existing terms</t>
+          <t>Notification window negotiated before Tavares set an internal 72-hour vendor standard; contract auto-renewed 2026-01-13 on existing terms</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
@@ -2229,7 +2230,7 @@
       </c>
       <c r="U20" s="15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="V20" s="15" t="inlineStr">
@@ -2317,7 +2318,7 @@
       </c>
       <c r="S21" s="15" t="inlineStr">
         <is>
-          <t>Obtain Vendor Risk Manager and Compliance Officer sign-off with a remediation plan before the 2026-04-01 renewal, or move archived records to a vendor that can evidence certified destruction</t>
+          <t>Obtain Vendor Risk Manager and Compliance Officer sign-off with a remediation plan before the 2026-04-07 renewal, or move archived records to a vendor that can evidence certified destruction</t>
         </is>
       </c>
       <c r="T21" s="15" t="inlineStr">
@@ -2327,7 +2328,7 @@
       </c>
       <c r="U21" s="15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="V21" s="15" t="inlineStr">
@@ -2735,7 +2736,7 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="11">
